--- a/dataset/01.w_Defects/func_pointer.xlsx
+++ b/dataset/01.w_Defects/func_pointer.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>int global_set=0; float ** doubleptr=NULL; extern volatile int vflag; void func_pointer_005() { int flag=0,i,j; long ** doubleptr=NULL; if(func_pointer_005_func_001(flag)==0) { void (*fptr)(void); fptr = (void (*)(void ))func_pointer_005_func_002; fptr();/*Tool should detect this line as error*/ /*ERROR:Bad function pointer casting*/ for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j] += 1; } free (doubleptr[i]); doubleptr[i] = NULL; } free(doubleptr); doubleptr = NULL; } } long ** func_pointer_005_func_002() { int i,j; long ** doubleptr; doubleptr=(long**) malloc(10*sizeof(long*)); for(i=0;i&lt;10;i++) { doubleptr[i]=(long*) malloc(10*sizeof(long)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j]=i; } } return doubleptr; } int func_pointer_005_func_001(int flag) { int ret =0; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>int global_set=0; float ** doubleptr=NULL; extern volatile int vflag; void func_pointer_005() { int flag=0,i,j; long ** doubleptr=NULL; if(func_pointer_005_func_001(flag)==0) { void (*fptr)(void); fptr = (void (*)(void ))func_pointer_005_func_002; fptr();/*Tool should detect this line as error*/ /*ERROR:Bad function pointer casting*/ for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j] += 1; } free (doubleptr[i]); doubleptr[i] = NULL; } free(doubleptr); doubleptr = NULL; } } int func_pointer_005_func_001(int flag) { int ret =0; if (flag ==0) ret = 0; else ret=1; return ret; } long ** func_pointer_005_func_002() { int i,j; long ** doubleptr; doubleptr=(long**) malloc(10*sizeof(long*)); for(i=0;i&lt;10;i++) { doubleptr[i]=(long*) malloc(10*sizeof(long)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j]=i; } } return doubleptr; }</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>int global_set=0; float ** doubleptr=NULL; extern volatile int vflag; void func_pointer_006() { int flag=0,i,j; if(func_pointer_006_func_001(flag)==0) { char **(*fptr)(); char **doubleptr; fptr = (char ** (*)(void))func_pointer_006_func_002; doubleptr = fptr();/*Tool should detect this line as error*/ /*ERROR:Bad function pointer casting*/ doubleptr = (char **)func_pointer_006_func_003(); for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j] += 1; } } doubleptr = (char **)func_pointer_006_func_004(); } } int func_pointer_006_func_001(int flag) { int ret =0; if (flag ==0) ret = 0; else ret=1; return ret; } float ** func_pointer_006_func_002() { int i,j; doubleptr=(float **) malloc(10*sizeof(float*)); for(i=0;i&lt;10;i++) { doubleptr[i]=(float *) malloc(10*sizeof(float)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j]=i; } } return doubleptr; } float ** func_pointer_006_func_004() { int i; for(i=0;i&lt;10;i++) { free (doubleptr[i]); doubleptr[i] = NULL; } free(doubleptr); doubleptr = NULL; return doubleptr; } float ** func_pointer_006_func_003() { int i,j; for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j]=i; } } return doubleptr; }</t>
+          <t>int global_set=0; float ** doubleptr=NULL; extern volatile int vflag; void func_pointer_006() { int flag=0,i,j; if(func_pointer_006_func_001(flag)==0) { char **(*fptr)(); char **doubleptr; fptr = (char ** (*)(void))func_pointer_006_func_002; doubleptr = fptr();/*Tool should detect this line as error*/ /*ERROR:Bad function pointer casting*/ doubleptr = (char **)func_pointer_006_func_003(); for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j] += 1; } } doubleptr = (char **)func_pointer_006_func_004(); } } float ** func_pointer_006_func_004() { int i; for(i=0;i&lt;10;i++) { free (doubleptr[i]); doubleptr[i] = NULL; } free(doubleptr); doubleptr = NULL; return doubleptr; } int func_pointer_006_func_001(int flag) { int ret =0; if (flag ==0) ret = 0; else ret=1; return ret; } float ** func_pointer_006_func_002() { int i,j; doubleptr=(float **) malloc(10*sizeof(float*)); for(i=0;i&lt;10;i++) { doubleptr[i]=(float *) malloc(10*sizeof(float)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j]=i; } } return doubleptr; } float ** func_pointer_006_func_003() { int i,j; for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { doubleptr[i][j]=i; } } return doubleptr; }</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>#define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } func_pointer_015_s_001; int global_set=0; float ** doubleptr=NULL; extern volatile int vflag; void func_pointer_015 () { func_pointer_015_s_001 st,*st1; st.a = 10; st1 = (func_pointer_015_s_001 *)malloc(1*sizeof(func_pointer_015_s_001)); memset(st1, 0, sizeof(*st1)); func_pointer_015_func_001(st1); void (*fptr3)(func_pointer_015_s_001* st1); fptr3 = func_pointer_015_func_004; fptr3(st1); } void func_pointer_015_func_001(func_pointer_015_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; global_set = 1; } void func_pointer_015_func_004(func_pointer_015_s_001* st1) { func_pointer_015_s_001 *st; if (global_set == MAX) { ; } else { fptr_gbl = (func_pointer_015_s_001 *(*)(func_pointer_015_s_001* ))func_pointer_015_func_003; st = fptr_gbl( st1);/*Tool should detect this line as error*/ /*ERROR:Bad function pointer casting*/ } } int func_pointer_015_func_003(func_pointer_015_s_001 *st) { st-&gt;b = st-&gt;c; return(st-&gt;b); }</t>
+          <t>#define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } func_pointer_015_s_001; int global_set=0; float ** doubleptr=NULL; extern volatile int vflag; void func_pointer_015 () { func_pointer_015_s_001 st,*st1; st.a = 10; st1 = (func_pointer_015_s_001 *)malloc(1*sizeof(func_pointer_015_s_001)); memset(st1, 0, sizeof(*st1)); func_pointer_015_func_001(st1); void (*fptr3)(func_pointer_015_s_001* st1); fptr3 = func_pointer_015_func_004; fptr3(st1); } void func_pointer_015_func_004(func_pointer_015_s_001* st1) { func_pointer_015_s_001 *st; if (global_set == MAX) { ; } else { fptr_gbl = (func_pointer_015_s_001 *(*)(func_pointer_015_s_001* ))func_pointer_015_func_003; st = fptr_gbl( st1);/*Tool should detect this line as error*/ /*ERROR:Bad function pointer casting*/ } } int func_pointer_015_func_003(func_pointer_015_s_001 *st) { st-&gt;b = st-&gt;c; return(st-&gt;b); } void func_pointer_015_func_001(func_pointer_015_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; global_set = 1; }</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
